--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/workout-session-controller/listMemberWorkoutSessions-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/workout-session-controller/listMemberWorkoutSessions-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
-  <si>
-    <t>Statement: workout-session-controller.listMemberWorkoutSessions(memberId, options?) – Server Action. No input validation. Delegates to workoutSessionService.listMemberWorkoutSessions(). Returns ActionResult&lt;PageResult&lt;WorkoutSessionWithExercises&gt;&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="84">
+  <si>
+    <t>Statement: listMemberWorkoutSessions(memberId, options?) – Lists workout sessions for a member and returns an ActionResult&lt;Page&lt;WorkoutSessionWithExercises&gt;&gt;. Returns success with a paginated page of sessions on success. Accepts an optional options object for filtering by date range (startDate, endDate) and for pagination (page, pageSize). When no pagination options are provided, sessions are returned in ascending date order. When pagination options are provided, sessions are returned in descending date order. Returns a failure with the service error message for AppError (e.g. NotFoundError).</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: memberId: string, options?: { startDate?, endDate?, page?, pageSize? }</t>
+    <t>Input: memberId: string, options?: WorkoutSessionListOptions { startDate?: Date, endDate?: Date, page?: number, pageSize?: number }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>workoutSessionService.listMemberWorkoutSessions is mock-injected</t>
+    <t>A known member id exists in the store. An empty memberId returns an empty page rather than an error. page: 0-based index; pageSize: minimum 1.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;PageResult&lt;WorkoutSessionWithExercises&gt;&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;Page&lt;WorkoutSessionWithExercises&gt;&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: page returned. On AppError: failure. On error: generic failure.</t>
+    <t>On success: sessions retrieved, returned data is a page with items and total. On AppError: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,37 +64,31 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>no extra options</t>
-  </si>
-  <si>
-    <t>service resolves page filtered by memberId</t>
-  </si>
-  <si>
-    <t>with date range</t>
-  </si>
-  <si>
-    <t>date range passed to service</t>
-  </si>
-  <si>
-    <t>empty sessions</t>
-  </si>
-  <si>
-    <t>items=[], total=0</t>
-  </si>
-  <si>
-    <t>pagination</t>
-  </si>
-  <si>
-    <t>pagination passed to service</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves page</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
+    <t>memberId validity</t>
+  </si>
+  <si>
+    <t>Known existing memberId → sessions retrieved successfully, returned page has items and total</t>
+  </si>
+  <si>
+    <t>options presence</t>
+  </si>
+  <si>
+    <t>Date range options provided (startDate, endDate) → sessions retrieved successfully</t>
+  </si>
+  <si>
+    <t>Sort order</t>
+  </si>
+  <si>
+    <t>Multiple sessions, no pagination options → sessions returned in ascending date order (older first)</t>
+  </si>
+  <si>
+    <t>Multiple sessions with pagination options → sessions returned in descending date order (newer first)</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>Member does not exist (NotFoundError "Member not found") → operation fails with message "Member not found"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -112,49 +106,52 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>memberId="member-001", no options</t>
-  </si>
-  <si>
-    <t>{ success: true, data.total: 1 }</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>memberId + { startDate, endDate }, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true }; listMemberWorkoutSessions(memberId, options) called</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>memberId, service resolves empty page</t>
-  </si>
-  <si>
-    <t>{ success: true, data.items: [] }</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>memberId + { page:2, pageSize:5 }, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true }; called with pagination</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>memberId, service throws Error("DB error")</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>known existing memberId, no options provided, one session exists</t>
+  </si>
+  <si>
+    <t>sessions retrieved successfully, returned page items has length 1 and total is 1</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>known existing memberId, options with startDate: new Date("2024-01-01") and endDate: new Date("2024-12-31") provided</t>
+  </si>
+  <si>
+    <t>sessions retrieved successfully</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>known existing memberId, no options provided, two sessions exist with dates "2024-01-01" (older) and "2024-12-31" (newer)</t>
+  </si>
+  <si>
+    <t>sessions retrieved successfully, first item has id "older", second item has id "newer"</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>known existing memberId, pagination options { page: 1, pageSize: 10 } provided, two sessions exist with dates "2024-01-01" (older) and "2024-12-01" (newer)</t>
+  </si>
+  <si>
+    <t>sessions retrieved successfully, first item has id "newer", second item has id "older"</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>known existing memberId, member does not exist (NotFoundError "Member not found")</t>
+  </si>
+  <si>
+    <t>operation fails with message "Member not found"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -163,16 +160,58 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>No sessions for member → total=0, items=[]</t>
+    <t>memberId length</t>
+  </si>
+  <si>
+    <t>memberId: "" (length 0): service returns empty page → sessions retrieved successfully, returned page items has length 0</t>
+  </si>
+  <si>
+    <t>memberId: "A" (length 1, min): shortest non-empty id → sessions retrieved successfully</t>
+  </si>
+  <si>
+    <t>page value</t>
+  </si>
+  <si>
+    <t>page: 0 (first page): valid boundary → sessions retrieved successfully</t>
+  </si>
+  <si>
+    <t>pageSize value</t>
+  </si>
+  <si>
+    <t>pageSize: 1 (minimum): one item per page → returned page items has length 1</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>empty result</t>
-  </si>
-  <si>
-    <t>memberId with no sessions</t>
+    <t>BVA-1 (memberId=0)</t>
+  </si>
+  <si>
+    <t>memberId: "" (empty string), service returns an empty page</t>
+  </si>
+  <si>
+    <t>sessions retrieved successfully, returned page items has length 0</t>
+  </si>
+  <si>
+    <t>BVA-2 (memberId=1)</t>
+  </si>
+  <si>
+    <t>memberId: "A" (1 character), service returns matching sessions successfully</t>
+  </si>
+  <si>
+    <t>BVA-3 (page=0)</t>
+  </si>
+  <si>
+    <t>known existing memberId, options: { page: 0 }, service returns the first page of sessions</t>
+  </si>
+  <si>
+    <t>BVA-4 (pageSize=1)</t>
+  </si>
+  <si>
+    <t>known existing memberId, options: { pageSize: 1 }, service returns a page with exactly one item</t>
+  </si>
+  <si>
+    <t>sessions retrieved successfully, returned page items has length 1</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -181,52 +220,16 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>memberId, no options</t>
-  </si>
-  <si>
-    <t>success=true, page returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>memberId + date range</t>
-  </si>
-  <si>
-    <t>success=true, service called with options</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>memberId, no sessions</t>
-  </si>
-  <si>
-    <t>success=true, items=[]</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>memberId + pagination</t>
-  </si>
-  <si>
-    <t>success=true, service called with pagination</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, "An unexpected error occurred"</t>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
   </si>
   <si>
     <t>Testing</t>
@@ -259,16 +262,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-05</t>
+    <t>CTRL-24</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -784,7 +784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -853,10 +853,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>1</v>
@@ -867,27 +867,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -910,19 +896,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -930,16 +916,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -947,16 +933,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -964,16 +950,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -981,16 +967,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -998,16 +984,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1018,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1028,13 +1014,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1042,10 +1028,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1068,19 +1087,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1088,16 +1107,67 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1121,22 +1191,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1144,19 +1214,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1164,19 +1234,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1184,19 +1254,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1204,19 +1274,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1224,19 +1294,99 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>69</v>
+      <c r="D9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1264,16 +1414,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1281,45 +1431,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>80</v>
+      <c r="A3" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="B3" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1328,19 +1478,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>83</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
